--- a/loan_data_cleaned.xlsx
+++ b/loan_data_cleaned.xlsx
@@ -2397,7 +2397,7 @@
         <v>45.1</v>
       </c>
       <c r="H58" t="n">
-        <v>75960</v>
+        <v>44200</v>
       </c>
       <c r="I58" t="n">
         <v>36</v>
@@ -5306,7 +5306,7 @@
         <v>39</v>
       </c>
       <c r="C144" t="n">
-        <v>341500</v>
+        <v>125550</v>
       </c>
       <c r="D144" t="n">
         <v>834</v>
@@ -5544,7 +5544,7 @@
         <v>41</v>
       </c>
       <c r="C151" t="n">
-        <v>136600</v>
+        <v>125550</v>
       </c>
       <c r="D151" t="n">
         <v>549</v>
@@ -7584,7 +7584,7 @@
         <v>25</v>
       </c>
       <c r="C211" t="n">
-        <v>134800</v>
+        <v>125550</v>
       </c>
       <c r="D211" t="n">
         <v>659</v>
@@ -10440,7 +10440,7 @@
         <v>36</v>
       </c>
       <c r="C295" t="n">
-        <v>341500</v>
+        <v>125550</v>
       </c>
       <c r="D295" t="n">
         <v>737</v>
@@ -11766,7 +11766,7 @@
         <v>44</v>
       </c>
       <c r="C334" t="n">
-        <v>125700</v>
+        <v>125550</v>
       </c>
       <c r="D334" t="n">
         <v>691</v>
@@ -14535,7 +14535,7 @@
         <v>37.8</v>
       </c>
       <c r="H415" t="n">
-        <v>75960</v>
+        <v>44200</v>
       </c>
       <c r="I415" t="n">
         <v>60</v>
